--- a/artfynd/S 875-2025 artfynd.xlsx
+++ b/artfynd/S 875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98167450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98167583</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/367120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143968</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143971</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107107075</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143980</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92206929</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92207109</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1920,6 +1975,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92207241</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2041,6 +2101,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92207421</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2165,6 +2230,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098543</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2289,6 +2359,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098605</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2413,6 +2488,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2542,6 +2622,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098894</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2658,6 +2743,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098992</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2759,6 +2849,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2193405</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2860,6 +2955,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2477228</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2961,6 +3061,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2660122</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3060,6 +3165,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2678181</t>
         </is>
       </c>
     </row>
@@ -3162,6 +3272,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143959</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3263,6 +3378,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3193995</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3362,6 +3482,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3794259</t>
         </is>
       </c>
     </row>
@@ -3464,6 +3589,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143956</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3566,6 +3696,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098713</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3667,6 +3802,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4690853</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3768,6 +3908,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4622306</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3867,6 +4012,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5010149</t>
         </is>
       </c>
     </row>
@@ -3971,6 +4121,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94098697</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4070,6 +4225,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5292066</t>
         </is>
       </c>
     </row>
@@ -4172,6 +4332,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61143998</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4280,6 +4445,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6569694</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4388,6 +4558,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6570193</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4495,8 +4670,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96125663</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>